--- a/public/Participants_QR_new.xlsx
+++ b/public/Participants_QR_new.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lenove\participants-app\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E311B59-CE8C-46A7-B9BB-11CD9B0DC308}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6B0AEF0-3CA7-4EAE-8613-C9ACF9B49848}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1663" uniqueCount="478">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1653" uniqueCount="476">
   <si>
     <t>Disciplines</t>
   </si>
@@ -1327,12 +1327,6 @@
   </si>
   <si>
     <t>wafaa.naji@veolia.com</t>
-  </si>
-  <si>
-    <t>BENABOUD Ikram</t>
-  </si>
-  <si>
-    <t>ikram.benaboud.ext@veolia.com</t>
   </si>
   <si>
     <t>blandine.chalet@veolia.com</t>
@@ -1760,7 +1754,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table_1" displayName="Table_1" ref="E138:I139" headerRowCount="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table_1" displayName="Table_1" ref="E137:I138" headerRowCount="0">
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Column1"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Column2"/>
@@ -1773,7 +1767,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Table_2" displayName="Table_2" ref="D147:I173" headerRowCount="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Table_2" displayName="Table_2" ref="D146:I172" headerRowCount="0">
   <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="Column1"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Column2"/>
@@ -1787,7 +1781,7 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="Table_3" displayName="Table_3" ref="E175:F180" headerRowCount="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="Table_3" displayName="Table_3" ref="E174:F179" headerRowCount="0">
   <tableColumns count="2">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="Column1"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="Column2"/>
@@ -1997,7 +1991,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:BM992"/>
+  <dimension ref="A1:BM991"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.77734375" customWidth="1"/>
@@ -12378,22 +12372,20 @@
     </row>
     <row r="120" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A120" s="18" t="s">
-        <v>209</v>
+        <v>110</v>
       </c>
       <c r="B120" s="19" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="C120" s="25" t="s">
         <v>27</v>
       </c>
       <c r="D120" s="19" t="s">
-        <v>435</v>
-      </c>
-      <c r="E120" s="19" t="s">
-        <v>436</v>
-      </c>
+        <v>288</v>
+      </c>
+      <c r="E120" s="19"/>
       <c r="F120" s="19" t="s">
-        <v>437</v>
+        <v>136</v>
       </c>
       <c r="G120" s="20">
         <v>46157</v>
@@ -12408,7 +12400,7 @@
         <v>65</v>
       </c>
       <c r="K120" s="22" t="s">
-        <v>371</v>
+        <v>162</v>
       </c>
       <c r="L120" s="19"/>
       <c r="M120" s="19"/>
@@ -12466,51 +12458,53 @@
       <c r="BM120" s="4"/>
     </row>
     <row r="121" spans="1:65" x14ac:dyDescent="0.25">
-      <c r="A121" s="18" t="s">
-        <v>110</v>
-      </c>
-      <c r="B121" s="19" t="s">
-        <v>438</v>
-      </c>
-      <c r="C121" s="25" t="s">
-        <v>27</v>
-      </c>
-      <c r="D121" s="19" t="s">
-        <v>288</v>
-      </c>
-      <c r="E121" s="19"/>
-      <c r="F121" s="19" t="s">
-        <v>136</v>
-      </c>
-      <c r="G121" s="20">
-        <v>46157</v>
-      </c>
-      <c r="H121" s="25" t="s">
+      <c r="A121" s="5" t="s">
+        <v>189</v>
+      </c>
+      <c r="B121" s="4" t="s">
+        <v>437</v>
+      </c>
+      <c r="C121" s="13" t="s">
+        <v>146</v>
+      </c>
+      <c r="D121" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="E121" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="F121" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="G121" s="7">
+        <v>46156</v>
+      </c>
+      <c r="H121" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="I121" s="21" t="s">
-        <v>102</v>
-      </c>
-      <c r="J121" s="22" t="s">
+      <c r="I121" s="9" t="s">
+        <v>191</v>
+      </c>
+      <c r="J121" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="K121" s="10" t="s">
         <v>65</v>
       </c>
-      <c r="K121" s="22" t="s">
-        <v>162</v>
-      </c>
-      <c r="L121" s="19"/>
-      <c r="M121" s="19"/>
-      <c r="N121" s="19"/>
-      <c r="O121" s="19"/>
-      <c r="P121" s="19"/>
-      <c r="Q121" s="19"/>
-      <c r="R121" s="19"/>
-      <c r="S121" s="19"/>
-      <c r="T121" s="19"/>
-      <c r="U121" s="19"/>
-      <c r="V121" s="19"/>
-      <c r="W121" s="19"/>
-      <c r="X121" s="19"/>
-      <c r="Y121" s="19"/>
+      <c r="L121" s="4"/>
+      <c r="M121" s="4"/>
+      <c r="N121" s="4"/>
+      <c r="O121" s="4"/>
+      <c r="P121" s="4"/>
+      <c r="Q121" s="4"/>
+      <c r="R121" s="4"/>
+      <c r="S121" s="4"/>
+      <c r="T121" s="4"/>
+      <c r="U121" s="4"/>
+      <c r="V121" s="4"/>
+      <c r="W121" s="4"/>
+      <c r="X121" s="4"/>
+      <c r="Y121" s="4"/>
       <c r="Z121" s="4"/>
       <c r="AA121" s="4"/>
       <c r="AB121" s="4"/>
@@ -12557,16 +12551,16 @@
         <v>189</v>
       </c>
       <c r="B122" s="4" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="C122" s="13" t="s">
         <v>146</v>
       </c>
       <c r="D122" s="4" t="s">
-        <v>162</v>
+        <v>256</v>
       </c>
       <c r="E122" s="4" t="s">
-        <v>246</v>
+        <v>257</v>
       </c>
       <c r="F122" s="4" t="s">
         <v>24</v>
@@ -12646,19 +12640,19 @@
         <v>189</v>
       </c>
       <c r="B123" s="4" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="C123" s="13" t="s">
-        <v>146</v>
+        <v>27</v>
       </c>
       <c r="D123" s="4" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="E123" s="4" t="s">
-        <v>257</v>
+        <v>29</v>
       </c>
       <c r="F123" s="4" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="G123" s="7">
         <v>46156</v>
@@ -12673,7 +12667,7 @@
         <v>9</v>
       </c>
       <c r="K123" s="10" t="s">
-        <v>65</v>
+        <v>371</v>
       </c>
       <c r="L123" s="4"/>
       <c r="M123" s="4"/>
@@ -12735,19 +12729,19 @@
         <v>189</v>
       </c>
       <c r="B124" s="4" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="C124" s="13" t="s">
         <v>27</v>
       </c>
       <c r="D124" s="4" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E124" s="4" t="s">
-        <v>29</v>
+        <v>260</v>
       </c>
       <c r="F124" s="4" t="s">
-        <v>30</v>
+        <v>261</v>
       </c>
       <c r="G124" s="7">
         <v>46156</v>
@@ -12824,19 +12818,19 @@
         <v>189</v>
       </c>
       <c r="B125" s="4" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="C125" s="13" t="s">
         <v>27</v>
       </c>
       <c r="D125" s="4" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="E125" s="4" t="s">
-        <v>260</v>
+        <v>434</v>
       </c>
       <c r="F125" s="4" t="s">
-        <v>261</v>
+        <v>435</v>
       </c>
       <c r="G125" s="7">
         <v>46156</v>
@@ -12913,19 +12907,19 @@
         <v>189</v>
       </c>
       <c r="B126" s="4" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="C126" s="13" t="s">
         <v>27</v>
       </c>
       <c r="D126" s="4" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="E126" s="4" t="s">
-        <v>436</v>
+        <v>31</v>
       </c>
       <c r="F126" s="4" t="s">
-        <v>437</v>
+        <v>24</v>
       </c>
       <c r="G126" s="7">
         <v>46156</v>
@@ -13002,13 +12996,13 @@
         <v>189</v>
       </c>
       <c r="B127" s="4" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="C127" s="13" t="s">
-        <v>27</v>
+        <v>264</v>
       </c>
       <c r="D127" s="4" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="E127" s="4" t="s">
         <v>31</v>
@@ -13091,16 +13085,14 @@
         <v>189</v>
       </c>
       <c r="B128" s="4" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="C128" s="13" t="s">
         <v>264</v>
       </c>
-      <c r="D128" s="4" t="s">
-        <v>265</v>
-      </c>
+      <c r="D128" s="4"/>
       <c r="E128" s="4" t="s">
-        <v>31</v>
+        <v>266</v>
       </c>
       <c r="F128" s="4" t="s">
         <v>24</v>
@@ -13118,7 +13110,7 @@
         <v>9</v>
       </c>
       <c r="K128" s="10" t="s">
-        <v>371</v>
+        <v>65</v>
       </c>
       <c r="L128" s="4"/>
       <c r="M128" s="4"/>
@@ -13177,35 +13169,35 @@
     </row>
     <row r="129" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A129" s="5" t="s">
-        <v>189</v>
+        <v>61</v>
       </c>
       <c r="B129" s="4" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="C129" s="13" t="s">
-        <v>264</v>
-      </c>
-      <c r="D129" s="4"/>
-      <c r="E129" s="4" t="s">
-        <v>266</v>
-      </c>
+        <v>27</v>
+      </c>
+      <c r="D129" s="4" t="s">
+        <v>267</v>
+      </c>
+      <c r="E129" s="4"/>
       <c r="F129" s="4" t="s">
-        <v>24</v>
+        <v>149</v>
       </c>
       <c r="G129" s="7">
-        <v>46156</v>
-      </c>
-      <c r="H129" s="8" t="s">
-        <v>7</v>
+        <v>46157</v>
+      </c>
+      <c r="H129" s="17" t="s">
+        <v>268</v>
       </c>
       <c r="I129" s="9" t="s">
-        <v>191</v>
+        <v>64</v>
       </c>
       <c r="J129" s="10" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="K129" s="10" t="s">
-        <v>65</v>
+        <v>162</v>
       </c>
       <c r="L129" s="4"/>
       <c r="M129" s="4"/>
@@ -13266,24 +13258,26 @@
       <c r="A130" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="B130" s="4" t="s">
-        <v>447</v>
-      </c>
-      <c r="C130" s="13" t="s">
-        <v>27</v>
-      </c>
-      <c r="D130" s="4" t="s">
-        <v>267</v>
-      </c>
-      <c r="E130" s="4"/>
-      <c r="F130" s="4" t="s">
-        <v>149</v>
+      <c r="B130" s="26" t="s">
+        <v>446</v>
+      </c>
+      <c r="C130" s="27" t="s">
+        <v>34</v>
+      </c>
+      <c r="D130" s="26" t="s">
+        <v>269</v>
+      </c>
+      <c r="E130" s="26" t="s">
+        <v>270</v>
+      </c>
+      <c r="F130" s="26" t="s">
+        <v>271</v>
       </c>
       <c r="G130" s="7">
         <v>46157</v>
       </c>
       <c r="H130" s="17" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="I130" s="9" t="s">
         <v>64</v>
@@ -13292,7 +13286,7 @@
         <v>65</v>
       </c>
       <c r="K130" s="10" t="s">
-        <v>162</v>
+        <v>371</v>
       </c>
       <c r="L130" s="4"/>
       <c r="M130" s="4"/>
@@ -13351,34 +13345,34 @@
     </row>
     <row r="131" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A131" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="B131" s="26" t="s">
-        <v>448</v>
-      </c>
-      <c r="C131" s="27" t="s">
-        <v>34</v>
-      </c>
-      <c r="D131" s="26" t="s">
-        <v>269</v>
-      </c>
-      <c r="E131" s="26" t="s">
-        <v>270</v>
-      </c>
-      <c r="F131" s="26" t="s">
-        <v>271</v>
+        <v>189</v>
+      </c>
+      <c r="B131" s="4" t="s">
+        <v>447</v>
+      </c>
+      <c r="C131" s="13" t="s">
+        <v>137</v>
+      </c>
+      <c r="D131" s="4" t="s">
+        <v>273</v>
+      </c>
+      <c r="E131" s="4" t="s">
+        <v>274</v>
+      </c>
+      <c r="F131" s="4" t="s">
+        <v>24</v>
       </c>
       <c r="G131" s="7">
-        <v>46157</v>
-      </c>
-      <c r="H131" s="17" t="s">
-        <v>272</v>
+        <v>46156</v>
+      </c>
+      <c r="H131" s="8" t="s">
+        <v>7</v>
       </c>
       <c r="I131" s="9" t="s">
-        <v>64</v>
+        <v>191</v>
       </c>
       <c r="J131" s="10" t="s">
-        <v>65</v>
+        <v>9</v>
       </c>
       <c r="K131" s="10" t="s">
         <v>371</v>
@@ -13443,16 +13437,16 @@
         <v>189</v>
       </c>
       <c r="B132" s="4" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="C132" s="13" t="s">
         <v>137</v>
       </c>
       <c r="D132" s="4" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="E132" s="4" t="s">
-        <v>274</v>
+        <v>138</v>
       </c>
       <c r="F132" s="4" t="s">
         <v>24</v>
@@ -13528,23 +13522,23 @@
       <c r="BM132" s="4"/>
     </row>
     <row r="133" spans="1:65" x14ac:dyDescent="0.25">
-      <c r="A133" s="5" t="s">
+      <c r="A133" s="14" t="s">
         <v>189</v>
       </c>
-      <c r="B133" s="4" t="s">
-        <v>450</v>
-      </c>
-      <c r="C133" s="13" t="s">
-        <v>137</v>
-      </c>
-      <c r="D133" s="4" t="s">
-        <v>275</v>
-      </c>
-      <c r="E133" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="F133" s="4" t="s">
-        <v>24</v>
+      <c r="B133" s="15" t="s">
+        <v>449</v>
+      </c>
+      <c r="C133" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="D133" s="15" t="s">
+        <v>276</v>
+      </c>
+      <c r="E133" s="15" t="s">
+        <v>40</v>
+      </c>
+      <c r="F133" s="15" t="s">
+        <v>277</v>
       </c>
       <c r="G133" s="7">
         <v>46156</v>
@@ -13617,53 +13611,53 @@
       <c r="BM133" s="4"/>
     </row>
     <row r="134" spans="1:65" x14ac:dyDescent="0.25">
-      <c r="A134" s="14" t="s">
+      <c r="A134" s="18" t="s">
         <v>189</v>
       </c>
-      <c r="B134" s="15" t="s">
+      <c r="B134" s="19" t="s">
+        <v>450</v>
+      </c>
+      <c r="C134" s="25" t="s">
+        <v>34</v>
+      </c>
+      <c r="D134" s="19" t="s">
         <v>451</v>
       </c>
-      <c r="C134" s="16" t="s">
-        <v>34</v>
-      </c>
-      <c r="D134" s="15" t="s">
-        <v>276</v>
-      </c>
-      <c r="E134" s="15" t="s">
+      <c r="E134" s="19" t="s">
         <v>40</v>
       </c>
-      <c r="F134" s="15" t="s">
+      <c r="F134" s="19" t="s">
         <v>277</v>
       </c>
-      <c r="G134" s="7">
+      <c r="G134" s="20">
         <v>46156</v>
       </c>
-      <c r="H134" s="8" t="s">
+      <c r="H134" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="I134" s="9" t="s">
+      <c r="I134" s="21" t="s">
         <v>191</v>
       </c>
-      <c r="J134" s="10" t="s">
+      <c r="J134" s="22" t="s">
         <v>9</v>
       </c>
-      <c r="K134" s="10" t="s">
+      <c r="K134" s="22" t="s">
         <v>371</v>
       </c>
-      <c r="L134" s="4"/>
-      <c r="M134" s="4"/>
-      <c r="N134" s="4"/>
-      <c r="O134" s="4"/>
-      <c r="P134" s="4"/>
-      <c r="Q134" s="4"/>
-      <c r="R134" s="4"/>
-      <c r="S134" s="4"/>
-      <c r="T134" s="4"/>
-      <c r="U134" s="4"/>
-      <c r="V134" s="4"/>
-      <c r="W134" s="4"/>
-      <c r="X134" s="4"/>
-      <c r="Y134" s="4"/>
+      <c r="L134" s="19"/>
+      <c r="M134" s="19"/>
+      <c r="N134" s="19"/>
+      <c r="O134" s="19"/>
+      <c r="P134" s="19"/>
+      <c r="Q134" s="19"/>
+      <c r="R134" s="19"/>
+      <c r="S134" s="19"/>
+      <c r="T134" s="19"/>
+      <c r="U134" s="19"/>
+      <c r="V134" s="19"/>
+      <c r="W134" s="19"/>
+      <c r="X134" s="19"/>
+      <c r="Y134" s="19"/>
       <c r="Z134" s="4"/>
       <c r="AA134" s="4"/>
       <c r="AB134" s="4"/>
@@ -13706,53 +13700,53 @@
       <c r="BM134" s="4"/>
     </row>
     <row r="135" spans="1:65" x14ac:dyDescent="0.25">
-      <c r="A135" s="18" t="s">
+      <c r="A135" s="14" t="s">
         <v>189</v>
       </c>
-      <c r="B135" s="19" t="s">
-        <v>452</v>
-      </c>
-      <c r="C135" s="25" t="s">
+      <c r="B135" s="15" t="s">
+        <v>279</v>
+      </c>
+      <c r="C135" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="D135" s="19" t="s">
-        <v>453</v>
-      </c>
-      <c r="E135" s="19" t="s">
-        <v>40</v>
-      </c>
-      <c r="F135" s="19" t="s">
-        <v>277</v>
-      </c>
-      <c r="G135" s="20">
+      <c r="D135" s="15" t="s">
+        <v>280</v>
+      </c>
+      <c r="E135" s="15" t="s">
+        <v>165</v>
+      </c>
+      <c r="F135" s="15" t="s">
+        <v>278</v>
+      </c>
+      <c r="G135" s="7">
         <v>46156</v>
       </c>
-      <c r="H135" s="25" t="s">
+      <c r="H135" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="I135" s="21" t="s">
+      <c r="I135" s="9" t="s">
         <v>191</v>
       </c>
-      <c r="J135" s="22" t="s">
+      <c r="J135" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="K135" s="22" t="s">
+      <c r="K135" s="10" t="s">
         <v>371</v>
       </c>
-      <c r="L135" s="19"/>
-      <c r="M135" s="19"/>
-      <c r="N135" s="19"/>
-      <c r="O135" s="19"/>
-      <c r="P135" s="19"/>
-      <c r="Q135" s="19"/>
-      <c r="R135" s="19"/>
-      <c r="S135" s="19"/>
-      <c r="T135" s="19"/>
-      <c r="U135" s="19"/>
-      <c r="V135" s="19"/>
-      <c r="W135" s="19"/>
-      <c r="X135" s="19"/>
-      <c r="Y135" s="19"/>
+      <c r="L135" s="4"/>
+      <c r="M135" s="4"/>
+      <c r="N135" s="4"/>
+      <c r="O135" s="4"/>
+      <c r="P135" s="4"/>
+      <c r="Q135" s="4"/>
+      <c r="R135" s="4"/>
+      <c r="S135" s="4"/>
+      <c r="T135" s="4"/>
+      <c r="U135" s="4"/>
+      <c r="V135" s="4"/>
+      <c r="W135" s="4"/>
+      <c r="X135" s="4"/>
+      <c r="Y135" s="4"/>
       <c r="Z135" s="4"/>
       <c r="AA135" s="4"/>
       <c r="AB135" s="4"/>
@@ -13795,53 +13789,53 @@
       <c r="BM135" s="4"/>
     </row>
     <row r="136" spans="1:65" x14ac:dyDescent="0.25">
-      <c r="A136" s="14" t="s">
+      <c r="A136" s="18" t="s">
         <v>189</v>
       </c>
-      <c r="B136" s="15" t="s">
-        <v>279</v>
-      </c>
-      <c r="C136" s="16" t="s">
+      <c r="B136" s="19" t="s">
+        <v>452</v>
+      </c>
+      <c r="C136" s="25" t="s">
         <v>34</v>
       </c>
-      <c r="D136" s="15" t="s">
-        <v>280</v>
-      </c>
-      <c r="E136" s="15" t="s">
-        <v>165</v>
-      </c>
-      <c r="F136" s="15" t="s">
-        <v>278</v>
-      </c>
-      <c r="G136" s="7">
+      <c r="D136" s="19" t="s">
+        <v>453</v>
+      </c>
+      <c r="E136" s="19" t="s">
+        <v>40</v>
+      </c>
+      <c r="F136" s="19" t="s">
+        <v>277</v>
+      </c>
+      <c r="G136" s="20">
         <v>46156</v>
       </c>
-      <c r="H136" s="8" t="s">
+      <c r="H136" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="I136" s="9" t="s">
+      <c r="I136" s="21" t="s">
         <v>191</v>
       </c>
-      <c r="J136" s="10" t="s">
+      <c r="J136" s="22" t="s">
         <v>9</v>
       </c>
-      <c r="K136" s="10" t="s">
+      <c r="K136" s="22" t="s">
         <v>371</v>
       </c>
-      <c r="L136" s="4"/>
-      <c r="M136" s="4"/>
-      <c r="N136" s="4"/>
-      <c r="O136" s="4"/>
-      <c r="P136" s="4"/>
-      <c r="Q136" s="4"/>
-      <c r="R136" s="4"/>
-      <c r="S136" s="4"/>
-      <c r="T136" s="4"/>
-      <c r="U136" s="4"/>
-      <c r="V136" s="4"/>
-      <c r="W136" s="4"/>
-      <c r="X136" s="4"/>
-      <c r="Y136" s="4"/>
+      <c r="L136" s="19"/>
+      <c r="M136" s="19"/>
+      <c r="N136" s="19"/>
+      <c r="O136" s="19"/>
+      <c r="P136" s="19"/>
+      <c r="Q136" s="19"/>
+      <c r="R136" s="19"/>
+      <c r="S136" s="19"/>
+      <c r="T136" s="19"/>
+      <c r="U136" s="19"/>
+      <c r="V136" s="19"/>
+      <c r="W136" s="19"/>
+      <c r="X136" s="19"/>
+      <c r="Y136" s="19"/>
       <c r="Z136" s="4"/>
       <c r="AA136" s="4"/>
       <c r="AB136" s="4"/>
@@ -13893,9 +13887,7 @@
       <c r="C137" s="25" t="s">
         <v>34</v>
       </c>
-      <c r="D137" s="19" t="s">
-        <v>455</v>
-      </c>
+      <c r="D137" s="19"/>
       <c r="E137" s="19" t="s">
         <v>40</v>
       </c>
@@ -13977,17 +13969,19 @@
         <v>189</v>
       </c>
       <c r="B138" s="19" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="C138" s="25" t="s">
         <v>34</v>
       </c>
-      <c r="D138" s="19"/>
+      <c r="D138" s="19" t="s">
+        <v>456</v>
+      </c>
       <c r="E138" s="19" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="F138" s="19" t="s">
-        <v>277</v>
+        <v>37</v>
       </c>
       <c r="G138" s="20">
         <v>46156</v>
@@ -14060,53 +14054,53 @@
       <c r="BM138" s="4"/>
     </row>
     <row r="139" spans="1:65" x14ac:dyDescent="0.25">
-      <c r="A139" s="18" t="s">
+      <c r="A139" s="14" t="s">
         <v>189</v>
       </c>
-      <c r="B139" s="19" t="s">
+      <c r="B139" s="15" t="s">
         <v>457</v>
       </c>
-      <c r="C139" s="25" t="s">
+      <c r="C139" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="D139" s="19" t="s">
-        <v>458</v>
-      </c>
-      <c r="E139" s="19" t="s">
-        <v>36</v>
-      </c>
-      <c r="F139" s="19" t="s">
-        <v>37</v>
-      </c>
-      <c r="G139" s="20">
+      <c r="D139" s="15" t="s">
+        <v>281</v>
+      </c>
+      <c r="E139" s="15" t="s">
+        <v>282</v>
+      </c>
+      <c r="F139" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="G139" s="7">
         <v>46156</v>
       </c>
-      <c r="H139" s="25" t="s">
+      <c r="H139" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="I139" s="21" t="s">
+      <c r="I139" s="9" t="s">
         <v>191</v>
       </c>
-      <c r="J139" s="22" t="s">
+      <c r="J139" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="K139" s="22" t="s">
+      <c r="K139" s="10" t="s">
         <v>371</v>
       </c>
-      <c r="L139" s="19"/>
-      <c r="M139" s="19"/>
-      <c r="N139" s="19"/>
-      <c r="O139" s="19"/>
-      <c r="P139" s="19"/>
-      <c r="Q139" s="19"/>
-      <c r="R139" s="19"/>
-      <c r="S139" s="19"/>
-      <c r="T139" s="19"/>
-      <c r="U139" s="19"/>
-      <c r="V139" s="19"/>
-      <c r="W139" s="19"/>
-      <c r="X139" s="19"/>
-      <c r="Y139" s="19"/>
+      <c r="L139" s="4"/>
+      <c r="M139" s="4"/>
+      <c r="N139" s="4"/>
+      <c r="O139" s="4"/>
+      <c r="P139" s="4"/>
+      <c r="Q139" s="4"/>
+      <c r="R139" s="4"/>
+      <c r="S139" s="4"/>
+      <c r="T139" s="4"/>
+      <c r="U139" s="4"/>
+      <c r="V139" s="4"/>
+      <c r="W139" s="4"/>
+      <c r="X139" s="4"/>
+      <c r="Y139" s="4"/>
       <c r="Z139" s="4"/>
       <c r="AA139" s="4"/>
       <c r="AB139" s="4"/>
@@ -14149,53 +14143,53 @@
       <c r="BM139" s="4"/>
     </row>
     <row r="140" spans="1:65" x14ac:dyDescent="0.25">
-      <c r="A140" s="14" t="s">
+      <c r="A140" s="18" t="s">
         <v>189</v>
       </c>
-      <c r="B140" s="15" t="s">
+      <c r="B140" s="19" t="s">
+        <v>458</v>
+      </c>
+      <c r="C140" s="25" t="s">
+        <v>34</v>
+      </c>
+      <c r="D140" s="19" t="s">
         <v>459</v>
       </c>
-      <c r="C140" s="16" t="s">
-        <v>34</v>
-      </c>
-      <c r="D140" s="15" t="s">
-        <v>281</v>
-      </c>
-      <c r="E140" s="15" t="s">
-        <v>282</v>
-      </c>
-      <c r="F140" s="15" t="s">
-        <v>50</v>
-      </c>
-      <c r="G140" s="7">
+      <c r="E140" s="19" t="s">
+        <v>119</v>
+      </c>
+      <c r="F140" s="19" t="s">
+        <v>60</v>
+      </c>
+      <c r="G140" s="20">
         <v>46156</v>
       </c>
-      <c r="H140" s="8" t="s">
+      <c r="H140" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="I140" s="9" t="s">
+      <c r="I140" s="21" t="s">
         <v>191</v>
       </c>
-      <c r="J140" s="10" t="s">
+      <c r="J140" s="22" t="s">
         <v>9</v>
       </c>
-      <c r="K140" s="10" t="s">
+      <c r="K140" s="22" t="s">
         <v>371</v>
       </c>
-      <c r="L140" s="4"/>
-      <c r="M140" s="4"/>
-      <c r="N140" s="4"/>
-      <c r="O140" s="4"/>
-      <c r="P140" s="4"/>
-      <c r="Q140" s="4"/>
-      <c r="R140" s="4"/>
-      <c r="S140" s="4"/>
-      <c r="T140" s="4"/>
-      <c r="U140" s="4"/>
-      <c r="V140" s="4"/>
-      <c r="W140" s="4"/>
-      <c r="X140" s="4"/>
-      <c r="Y140" s="4"/>
+      <c r="L140" s="19"/>
+      <c r="M140" s="19"/>
+      <c r="N140" s="19"/>
+      <c r="O140" s="19"/>
+      <c r="P140" s="19"/>
+      <c r="Q140" s="19"/>
+      <c r="R140" s="19"/>
+      <c r="S140" s="19"/>
+      <c r="T140" s="19"/>
+      <c r="U140" s="19"/>
+      <c r="V140" s="19"/>
+      <c r="W140" s="19"/>
+      <c r="X140" s="19"/>
+      <c r="Y140" s="19"/>
       <c r="Z140" s="4"/>
       <c r="AA140" s="4"/>
       <c r="AB140" s="4"/>
@@ -14238,53 +14232,51 @@
       <c r="BM140" s="4"/>
     </row>
     <row r="141" spans="1:65" x14ac:dyDescent="0.25">
-      <c r="A141" s="18" t="s">
-        <v>189</v>
-      </c>
-      <c r="B141" s="19" t="s">
+      <c r="A141" s="5" t="s">
+        <v>283</v>
+      </c>
+      <c r="B141" s="6" t="s">
         <v>460</v>
       </c>
-      <c r="C141" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="D141" s="19" t="s">
-        <v>461</v>
-      </c>
-      <c r="E141" s="19" t="s">
-        <v>119</v>
-      </c>
-      <c r="F141" s="19" t="s">
-        <v>60</v>
-      </c>
-      <c r="G141" s="20">
+      <c r="C141" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="D141" s="6" t="s">
+        <v>284</v>
+      </c>
+      <c r="E141" s="6" t="s">
+        <v>228</v>
+      </c>
+      <c r="F141" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="G141" s="7">
         <v>46156</v>
       </c>
-      <c r="H141" s="25" t="s">
+      <c r="H141" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="I141" s="21" t="s">
-        <v>191</v>
-      </c>
-      <c r="J141" s="22" t="s">
+      <c r="I141" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="J141" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="K141" s="22" t="s">
-        <v>371</v>
-      </c>
-      <c r="L141" s="19"/>
-      <c r="M141" s="19"/>
-      <c r="N141" s="19"/>
-      <c r="O141" s="19"/>
-      <c r="P141" s="19"/>
-      <c r="Q141" s="19"/>
-      <c r="R141" s="19"/>
-      <c r="S141" s="19"/>
-      <c r="T141" s="19"/>
-      <c r="U141" s="19"/>
-      <c r="V141" s="19"/>
-      <c r="W141" s="19"/>
-      <c r="X141" s="19"/>
-      <c r="Y141" s="19"/>
+      <c r="K141" s="10"/>
+      <c r="L141" s="4"/>
+      <c r="M141" s="4"/>
+      <c r="N141" s="4"/>
+      <c r="O141" s="4"/>
+      <c r="P141" s="4"/>
+      <c r="Q141" s="4"/>
+      <c r="R141" s="4"/>
+      <c r="S141" s="4"/>
+      <c r="T141" s="4"/>
+      <c r="U141" s="4"/>
+      <c r="V141" s="4"/>
+      <c r="W141" s="4"/>
+      <c r="X141" s="4"/>
+      <c r="Y141" s="4"/>
       <c r="Z141" s="4"/>
       <c r="AA141" s="4"/>
       <c r="AB141" s="4"/>
@@ -14327,23 +14319,23 @@
       <c r="BM141" s="4"/>
     </row>
     <row r="142" spans="1:65" x14ac:dyDescent="0.25">
-      <c r="A142" s="5" t="s">
+      <c r="A142" s="11" t="s">
         <v>283</v>
       </c>
-      <c r="B142" s="6" t="s">
-        <v>462</v>
-      </c>
-      <c r="C142" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="D142" s="6" t="s">
-        <v>284</v>
-      </c>
-      <c r="E142" s="6" t="s">
-        <v>228</v>
-      </c>
-      <c r="F142" s="6" t="s">
-        <v>50</v>
+      <c r="B142" s="12" t="s">
+        <v>285</v>
+      </c>
+      <c r="C142" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="D142" s="12" t="s">
+        <v>156</v>
+      </c>
+      <c r="E142" s="12" t="s">
+        <v>133</v>
+      </c>
+      <c r="F142" s="12" t="s">
+        <v>17</v>
       </c>
       <c r="G142" s="7">
         <v>46156</v>
@@ -14414,23 +14406,23 @@
       <c r="BM142" s="4"/>
     </row>
     <row r="143" spans="1:65" x14ac:dyDescent="0.25">
-      <c r="A143" s="11" t="s">
+      <c r="A143" s="5" t="s">
         <v>283</v>
       </c>
-      <c r="B143" s="12" t="s">
-        <v>285</v>
-      </c>
-      <c r="C143" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="D143" s="12" t="s">
-        <v>156</v>
-      </c>
-      <c r="E143" s="12" t="s">
-        <v>133</v>
-      </c>
-      <c r="F143" s="12" t="s">
-        <v>17</v>
+      <c r="B143" s="4" t="s">
+        <v>461</v>
+      </c>
+      <c r="C143" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="D143" s="4" t="s">
+        <v>286</v>
+      </c>
+      <c r="E143" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="F143" s="4" t="s">
+        <v>24</v>
       </c>
       <c r="G143" s="7">
         <v>46156</v>
@@ -14444,7 +14436,9 @@
       <c r="J143" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="K143" s="10"/>
+      <c r="K143" s="10" t="s">
+        <v>65</v>
+      </c>
       <c r="L143" s="4"/>
       <c r="M143" s="4"/>
       <c r="N143" s="4"/>
@@ -14505,13 +14499,13 @@
         <v>283</v>
       </c>
       <c r="B144" s="4" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="C144" s="13" t="s">
         <v>21</v>
       </c>
       <c r="D144" s="4" t="s">
-        <v>286</v>
+        <v>162</v>
       </c>
       <c r="E144" s="4" t="s">
         <v>23</v>
@@ -14594,19 +14588,19 @@
         <v>283</v>
       </c>
       <c r="B145" s="4" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="C145" s="13" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="D145" s="4" t="s">
-        <v>162</v>
+        <v>287</v>
       </c>
       <c r="E145" s="4" t="s">
-        <v>23</v>
+        <v>288</v>
       </c>
       <c r="F145" s="4" t="s">
-        <v>24</v>
+        <v>136</v>
       </c>
       <c r="G145" s="7">
         <v>46156</v>
@@ -14614,14 +14608,14 @@
       <c r="H145" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="I145" s="4" t="s">
+      <c r="I145" s="9" t="s">
         <v>8</v>
       </c>
       <c r="J145" s="10" t="s">
         <v>9</v>
       </c>
       <c r="K145" s="10" t="s">
-        <v>65</v>
+        <v>371</v>
       </c>
       <c r="L145" s="4"/>
       <c r="M145" s="4"/>
@@ -14679,23 +14673,23 @@
       <c r="BM145" s="4"/>
     </row>
     <row r="146" spans="1:65" x14ac:dyDescent="0.25">
-      <c r="A146" s="5" t="s">
+      <c r="A146" s="14" t="s">
         <v>283</v>
       </c>
-      <c r="B146" s="4" t="s">
-        <v>465</v>
-      </c>
-      <c r="C146" s="13" t="s">
-        <v>27</v>
-      </c>
-      <c r="D146" s="4" t="s">
-        <v>287</v>
-      </c>
-      <c r="E146" s="4" t="s">
-        <v>288</v>
-      </c>
-      <c r="F146" s="4" t="s">
-        <v>136</v>
+      <c r="B146" s="15" t="s">
+        <v>289</v>
+      </c>
+      <c r="C146" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="D146" s="15" t="s">
+        <v>290</v>
+      </c>
+      <c r="E146" s="15" t="s">
+        <v>291</v>
+      </c>
+      <c r="F146" s="15" t="s">
+        <v>17</v>
       </c>
       <c r="G146" s="7">
         <v>46156</v>
@@ -14768,23 +14762,23 @@
       <c r="BM146" s="4"/>
     </row>
     <row r="147" spans="1:65" x14ac:dyDescent="0.25">
-      <c r="A147" s="14" t="s">
-        <v>283</v>
-      </c>
-      <c r="B147" s="15" t="s">
-        <v>289</v>
-      </c>
-      <c r="C147" s="16" t="s">
-        <v>34</v>
-      </c>
-      <c r="D147" s="15" t="s">
-        <v>290</v>
-      </c>
-      <c r="E147" s="15" t="s">
-        <v>291</v>
-      </c>
-      <c r="F147" s="15" t="s">
-        <v>17</v>
+      <c r="A147" s="5" t="s">
+        <v>292</v>
+      </c>
+      <c r="B147" s="6" t="s">
+        <v>464</v>
+      </c>
+      <c r="C147" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="D147" s="6" t="s">
+        <v>293</v>
+      </c>
+      <c r="E147" s="6" t="s">
+        <v>294</v>
+      </c>
+      <c r="F147" s="6" t="s">
+        <v>6</v>
       </c>
       <c r="G147" s="7">
         <v>46156</v>
@@ -14798,9 +14792,7 @@
       <c r="J147" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="K147" s="10" t="s">
-        <v>371</v>
-      </c>
+      <c r="K147" s="10"/>
       <c r="L147" s="4"/>
       <c r="M147" s="4"/>
       <c r="N147" s="4"/>
@@ -14857,23 +14849,23 @@
       <c r="BM147" s="4"/>
     </row>
     <row r="148" spans="1:65" x14ac:dyDescent="0.25">
-      <c r="A148" s="5" t="s">
+      <c r="A148" s="11" t="s">
         <v>292</v>
       </c>
-      <c r="B148" s="6" t="s">
-        <v>466</v>
-      </c>
-      <c r="C148" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="D148" s="6" t="s">
-        <v>293</v>
-      </c>
-      <c r="E148" s="6" t="s">
-        <v>294</v>
-      </c>
-      <c r="F148" s="6" t="s">
-        <v>6</v>
+      <c r="B148" s="12" t="s">
+        <v>295</v>
+      </c>
+      <c r="C148" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="D148" s="12" t="s">
+        <v>296</v>
+      </c>
+      <c r="E148" s="12" t="s">
+        <v>297</v>
+      </c>
+      <c r="F148" s="12" t="s">
+        <v>12</v>
       </c>
       <c r="G148" s="7">
         <v>46156</v>
@@ -14944,23 +14936,23 @@
       <c r="BM148" s="4"/>
     </row>
     <row r="149" spans="1:65" x14ac:dyDescent="0.25">
-      <c r="A149" s="11" t="s">
+      <c r="A149" s="5" t="s">
         <v>292</v>
       </c>
-      <c r="B149" s="12" t="s">
-        <v>295</v>
-      </c>
-      <c r="C149" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="D149" s="12" t="s">
-        <v>296</v>
-      </c>
-      <c r="E149" s="12" t="s">
-        <v>297</v>
-      </c>
-      <c r="F149" s="12" t="s">
-        <v>12</v>
+      <c r="B149" s="4" t="s">
+        <v>465</v>
+      </c>
+      <c r="C149" s="13" t="s">
+        <v>146</v>
+      </c>
+      <c r="D149" s="28" t="s">
+        <v>249</v>
+      </c>
+      <c r="E149" s="28" t="s">
+        <v>298</v>
+      </c>
+      <c r="F149" s="28" t="s">
+        <v>149</v>
       </c>
       <c r="G149" s="7">
         <v>46156</v>
@@ -14974,7 +14966,9 @@
       <c r="J149" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="K149" s="10"/>
+      <c r="K149" s="10" t="s">
+        <v>65</v>
+      </c>
       <c r="L149" s="4"/>
       <c r="M149" s="4"/>
       <c r="N149" s="4"/>
@@ -15035,19 +15029,19 @@
         <v>292</v>
       </c>
       <c r="B150" s="4" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="C150" s="13" t="s">
-        <v>146</v>
-      </c>
-      <c r="D150" s="28" t="s">
-        <v>249</v>
-      </c>
-      <c r="E150" s="28" t="s">
-        <v>298</v>
-      </c>
-      <c r="F150" s="28" t="s">
-        <v>149</v>
+        <v>27</v>
+      </c>
+      <c r="D150" s="29" t="s">
+        <v>299</v>
+      </c>
+      <c r="E150" s="29" t="s">
+        <v>267</v>
+      </c>
+      <c r="F150" s="29" t="s">
+        <v>30</v>
       </c>
       <c r="G150" s="7">
         <v>46156</v>
@@ -15062,7 +15056,7 @@
         <v>9</v>
       </c>
       <c r="K150" s="10" t="s">
-        <v>65</v>
+        <v>371</v>
       </c>
       <c r="L150" s="4"/>
       <c r="M150" s="4"/>
@@ -15120,23 +15114,21 @@
       <c r="BM150" s="4"/>
     </row>
     <row r="151" spans="1:65" x14ac:dyDescent="0.25">
-      <c r="A151" s="5" t="s">
+      <c r="A151" s="24" t="s">
         <v>292</v>
       </c>
-      <c r="B151" s="4" t="s">
-        <v>468</v>
-      </c>
-      <c r="C151" s="13" t="s">
-        <v>27</v>
-      </c>
-      <c r="D151" s="29" t="s">
-        <v>299</v>
-      </c>
-      <c r="E151" s="29" t="s">
-        <v>267</v>
-      </c>
-      <c r="F151" s="29" t="s">
-        <v>30</v>
+      <c r="B151" s="15" t="s">
+        <v>300</v>
+      </c>
+      <c r="C151" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="D151" s="15"/>
+      <c r="E151" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="F151" s="15" t="s">
+        <v>37</v>
       </c>
       <c r="G151" s="7">
         <v>46156</v>
@@ -15209,33 +15201,35 @@
       <c r="BM151" s="4"/>
     </row>
     <row r="152" spans="1:65" x14ac:dyDescent="0.25">
-      <c r="A152" s="24" t="s">
-        <v>292</v>
+      <c r="A152" s="14" t="s">
+        <v>61</v>
       </c>
       <c r="B152" s="15" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C152" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="D152" s="15"/>
+      <c r="D152" s="15" t="s">
+        <v>302</v>
+      </c>
       <c r="E152" s="15" t="s">
-        <v>36</v>
+        <v>303</v>
       </c>
       <c r="F152" s="15" t="s">
-        <v>37</v>
+        <v>76</v>
       </c>
       <c r="G152" s="7">
-        <v>46156</v>
-      </c>
-      <c r="H152" s="8" t="s">
-        <v>7</v>
+        <v>46157</v>
+      </c>
+      <c r="H152" s="17" t="s">
+        <v>304</v>
       </c>
       <c r="I152" s="9" t="s">
-        <v>8</v>
+        <v>64</v>
       </c>
       <c r="J152" s="10" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="K152" s="10" t="s">
         <v>371</v>
@@ -15300,25 +15294,25 @@
         <v>61</v>
       </c>
       <c r="B153" s="15" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="C153" s="16" t="s">
         <v>34</v>
       </c>
       <c r="D153" s="15" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="E153" s="15" t="s">
-        <v>303</v>
+        <v>270</v>
       </c>
       <c r="F153" s="15" t="s">
-        <v>76</v>
+        <v>271</v>
       </c>
       <c r="G153" s="7">
         <v>46157</v>
       </c>
       <c r="H153" s="17" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="I153" s="9" t="s">
         <v>64</v>
@@ -15385,39 +15379,37 @@
       <c r="BM153" s="4"/>
     </row>
     <row r="154" spans="1:65" x14ac:dyDescent="0.25">
-      <c r="A154" s="14" t="s">
-        <v>61</v>
-      </c>
-      <c r="B154" s="15" t="s">
-        <v>305</v>
-      </c>
-      <c r="C154" s="16" t="s">
-        <v>34</v>
-      </c>
-      <c r="D154" s="15" t="s">
-        <v>306</v>
-      </c>
-      <c r="E154" s="15" t="s">
-        <v>270</v>
-      </c>
-      <c r="F154" s="15" t="s">
-        <v>271</v>
+      <c r="A154" s="11" t="s">
+        <v>308</v>
+      </c>
+      <c r="B154" s="12" t="s">
+        <v>309</v>
+      </c>
+      <c r="C154" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="D154" s="12" t="s">
+        <v>310</v>
+      </c>
+      <c r="E154" s="12" t="s">
+        <v>311</v>
+      </c>
+      <c r="F154" s="12" t="s">
+        <v>312</v>
       </c>
       <c r="G154" s="7">
-        <v>46157</v>
-      </c>
-      <c r="H154" s="17" t="s">
-        <v>307</v>
+        <v>46156</v>
+      </c>
+      <c r="H154" s="8" t="s">
+        <v>7</v>
       </c>
       <c r="I154" s="9" t="s">
-        <v>64</v>
+        <v>8</v>
       </c>
       <c r="J154" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="K154" s="10" t="s">
-        <v>371</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="K154" s="10"/>
       <c r="L154" s="4"/>
       <c r="M154" s="4"/>
       <c r="N154" s="4"/>
@@ -15474,23 +15466,23 @@
       <c r="BM154" s="4"/>
     </row>
     <row r="155" spans="1:65" x14ac:dyDescent="0.25">
-      <c r="A155" s="11" t="s">
+      <c r="A155" s="14" t="s">
         <v>308</v>
       </c>
-      <c r="B155" s="12" t="s">
-        <v>309</v>
-      </c>
-      <c r="C155" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="D155" s="12" t="s">
-        <v>310</v>
-      </c>
-      <c r="E155" s="12" t="s">
-        <v>311</v>
-      </c>
-      <c r="F155" s="12" t="s">
-        <v>312</v>
+      <c r="B155" s="15" t="s">
+        <v>313</v>
+      </c>
+      <c r="C155" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="D155" s="15" t="s">
+        <v>314</v>
+      </c>
+      <c r="E155" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="F155" s="15" t="s">
+        <v>76</v>
       </c>
       <c r="G155" s="7">
         <v>46156</v>
@@ -15504,7 +15496,9 @@
       <c r="J155" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="K155" s="10"/>
+      <c r="K155" s="10" t="s">
+        <v>371</v>
+      </c>
       <c r="L155" s="4"/>
       <c r="M155" s="4"/>
       <c r="N155" s="4"/>
@@ -15561,23 +15555,23 @@
       <c r="BM155" s="4"/>
     </row>
     <row r="156" spans="1:65" x14ac:dyDescent="0.25">
-      <c r="A156" s="14" t="s">
-        <v>308</v>
-      </c>
-      <c r="B156" s="15" t="s">
-        <v>313</v>
-      </c>
-      <c r="C156" s="16" t="s">
-        <v>34</v>
-      </c>
-      <c r="D156" s="15" t="s">
-        <v>314</v>
-      </c>
-      <c r="E156" s="15" t="s">
-        <v>75</v>
-      </c>
-      <c r="F156" s="15" t="s">
-        <v>76</v>
+      <c r="A156" s="5" t="s">
+        <v>315</v>
+      </c>
+      <c r="B156" s="6" t="s">
+        <v>467</v>
+      </c>
+      <c r="C156" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="D156" s="6" t="s">
+        <v>316</v>
+      </c>
+      <c r="E156" s="6" t="s">
+        <v>317</v>
+      </c>
+      <c r="F156" s="6" t="s">
+        <v>71</v>
       </c>
       <c r="G156" s="7">
         <v>46156</v>
@@ -15591,9 +15585,7 @@
       <c r="J156" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="K156" s="10" t="s">
-        <v>371</v>
-      </c>
+      <c r="K156" s="10"/>
       <c r="L156" s="4"/>
       <c r="M156" s="4"/>
       <c r="N156" s="4"/>
@@ -15650,23 +15642,23 @@
       <c r="BM156" s="4"/>
     </row>
     <row r="157" spans="1:65" x14ac:dyDescent="0.25">
-      <c r="A157" s="5" t="s">
+      <c r="A157" s="11" t="s">
         <v>315</v>
       </c>
-      <c r="B157" s="6" t="s">
-        <v>469</v>
-      </c>
-      <c r="C157" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="D157" s="6" t="s">
-        <v>316</v>
-      </c>
-      <c r="E157" s="6" t="s">
-        <v>317</v>
-      </c>
-      <c r="F157" s="6" t="s">
-        <v>71</v>
+      <c r="B157" s="12" t="s">
+        <v>318</v>
+      </c>
+      <c r="C157" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="D157" s="12" t="s">
+        <v>319</v>
+      </c>
+      <c r="E157" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="F157" s="12" t="s">
+        <v>50</v>
       </c>
       <c r="G157" s="7">
         <v>46156</v>
@@ -15737,23 +15729,23 @@
       <c r="BM157" s="4"/>
     </row>
     <row r="158" spans="1:65" x14ac:dyDescent="0.25">
-      <c r="A158" s="11" t="s">
+      <c r="A158" s="14" t="s">
         <v>315</v>
       </c>
-      <c r="B158" s="12" t="s">
-        <v>318</v>
-      </c>
-      <c r="C158" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="D158" s="12" t="s">
-        <v>319</v>
-      </c>
-      <c r="E158" s="12" t="s">
-        <v>49</v>
-      </c>
-      <c r="F158" s="12" t="s">
-        <v>50</v>
+      <c r="B158" s="15" t="s">
+        <v>320</v>
+      </c>
+      <c r="C158" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="D158" s="15" t="s">
+        <v>321</v>
+      </c>
+      <c r="E158" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="F158" s="15" t="s">
+        <v>76</v>
       </c>
       <c r="G158" s="7">
         <v>46156</v>
@@ -15767,7 +15759,9 @@
       <c r="J158" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="K158" s="10"/>
+      <c r="K158" s="10" t="s">
+        <v>371</v>
+      </c>
       <c r="L158" s="4"/>
       <c r="M158" s="4"/>
       <c r="N158" s="4"/>
@@ -15824,23 +15818,23 @@
       <c r="BM158" s="4"/>
     </row>
     <row r="159" spans="1:65" x14ac:dyDescent="0.25">
-      <c r="A159" s="14" t="s">
-        <v>315</v>
-      </c>
-      <c r="B159" s="15" t="s">
-        <v>320</v>
-      </c>
-      <c r="C159" s="16" t="s">
-        <v>34</v>
-      </c>
-      <c r="D159" s="15" t="s">
-        <v>321</v>
-      </c>
-      <c r="E159" s="15" t="s">
-        <v>75</v>
-      </c>
-      <c r="F159" s="15" t="s">
-        <v>76</v>
+      <c r="A159" s="5" t="s">
+        <v>322</v>
+      </c>
+      <c r="B159" s="6" t="s">
+        <v>468</v>
+      </c>
+      <c r="C159" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="D159" s="6" t="s">
+        <v>323</v>
+      </c>
+      <c r="E159" s="6" t="s">
+        <v>324</v>
+      </c>
+      <c r="F159" s="6" t="s">
+        <v>325</v>
       </c>
       <c r="G159" s="7">
         <v>46156</v>
@@ -15854,9 +15848,7 @@
       <c r="J159" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="K159" s="10" t="s">
-        <v>371</v>
-      </c>
+      <c r="K159" s="10"/>
       <c r="L159" s="4"/>
       <c r="M159" s="4"/>
       <c r="N159" s="4"/>
@@ -15917,19 +15909,17 @@
         <v>322</v>
       </c>
       <c r="B160" s="6" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="C160" s="6" t="s">
         <v>3</v>
       </c>
       <c r="D160" s="6" t="s">
-        <v>323</v>
-      </c>
-      <c r="E160" s="6" t="s">
-        <v>324</v>
-      </c>
+        <v>326</v>
+      </c>
+      <c r="E160" s="6"/>
       <c r="F160" s="6" t="s">
-        <v>325</v>
+        <v>17</v>
       </c>
       <c r="G160" s="7">
         <v>46156</v>
@@ -16004,17 +15994,17 @@
         <v>322</v>
       </c>
       <c r="B161" s="6" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="C161" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="D161" s="6" t="s">
-        <v>326</v>
-      </c>
-      <c r="E161" s="6"/>
+      <c r="D161" s="6"/>
+      <c r="E161" s="6" t="s">
+        <v>228</v>
+      </c>
       <c r="F161" s="6" t="s">
-        <v>17</v>
+        <v>50</v>
       </c>
       <c r="G161" s="7">
         <v>46156</v>
@@ -16089,14 +16079,16 @@
         <v>322</v>
       </c>
       <c r="B162" s="6" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="C162" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="D162" s="6"/>
+      <c r="D162" s="6" t="s">
+        <v>327</v>
+      </c>
       <c r="E162" s="6" t="s">
-        <v>228</v>
+        <v>328</v>
       </c>
       <c r="F162" s="6" t="s">
         <v>50</v>
@@ -16170,23 +16162,23 @@
       <c r="BM162" s="4"/>
     </row>
     <row r="163" spans="1:65" x14ac:dyDescent="0.25">
-      <c r="A163" s="5" t="s">
+      <c r="A163" s="11" t="s">
         <v>322</v>
       </c>
-      <c r="B163" s="6" t="s">
-        <v>473</v>
-      </c>
-      <c r="C163" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="D163" s="6" t="s">
-        <v>327</v>
-      </c>
-      <c r="E163" s="6" t="s">
-        <v>328</v>
-      </c>
-      <c r="F163" s="6" t="s">
-        <v>50</v>
+      <c r="B163" s="12" t="s">
+        <v>329</v>
+      </c>
+      <c r="C163" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="D163" s="12" t="s">
+        <v>330</v>
+      </c>
+      <c r="E163" s="12" t="s">
+        <v>311</v>
+      </c>
+      <c r="F163" s="12" t="s">
+        <v>312</v>
       </c>
       <c r="G163" s="7">
         <v>46156</v>
@@ -16261,19 +16253,19 @@
         <v>322</v>
       </c>
       <c r="B164" s="12" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="C164" s="8" t="s">
         <v>14</v>
       </c>
       <c r="D164" s="12" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="E164" s="12" t="s">
-        <v>311</v>
+        <v>297</v>
       </c>
       <c r="F164" s="12" t="s">
-        <v>312</v>
+        <v>12</v>
       </c>
       <c r="G164" s="7">
         <v>46156</v>
@@ -16348,19 +16340,19 @@
         <v>322</v>
       </c>
       <c r="B165" s="12" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="C165" s="8" t="s">
         <v>14</v>
       </c>
       <c r="D165" s="12" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="E165" s="12" t="s">
-        <v>297</v>
+        <v>207</v>
       </c>
       <c r="F165" s="12" t="s">
-        <v>12</v>
+        <v>71</v>
       </c>
       <c r="G165" s="7">
         <v>46156</v>
@@ -16435,19 +16427,19 @@
         <v>322</v>
       </c>
       <c r="B166" s="12" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="C166" s="8" t="s">
         <v>14</v>
       </c>
       <c r="D166" s="12" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="E166" s="12" t="s">
-        <v>207</v>
+        <v>337</v>
       </c>
       <c r="F166" s="12" t="s">
-        <v>71</v>
+        <v>12</v>
       </c>
       <c r="G166" s="7">
         <v>46156</v>
@@ -16518,23 +16510,23 @@
       <c r="BM166" s="4"/>
     </row>
     <row r="167" spans="1:65" x14ac:dyDescent="0.25">
-      <c r="A167" s="11" t="s">
+      <c r="A167" s="14" t="s">
         <v>322</v>
       </c>
-      <c r="B167" s="12" t="s">
-        <v>335</v>
-      </c>
-      <c r="C167" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="D167" s="12" t="s">
-        <v>336</v>
-      </c>
-      <c r="E167" s="12" t="s">
-        <v>337</v>
-      </c>
-      <c r="F167" s="12" t="s">
-        <v>12</v>
+      <c r="B167" s="15" t="s">
+        <v>338</v>
+      </c>
+      <c r="C167" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="D167" s="15" t="s">
+        <v>339</v>
+      </c>
+      <c r="E167" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="F167" s="15" t="s">
+        <v>37</v>
       </c>
       <c r="G167" s="7">
         <v>46156</v>
@@ -16548,7 +16540,9 @@
       <c r="J167" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="K167" s="10"/>
+      <c r="K167" s="10" t="s">
+        <v>371</v>
+      </c>
       <c r="L167" s="4"/>
       <c r="M167" s="4"/>
       <c r="N167" s="4"/>
@@ -16609,14 +16603,12 @@
         <v>322</v>
       </c>
       <c r="B168" s="15" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="C168" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="D168" s="15" t="s">
-        <v>339</v>
-      </c>
+      <c r="D168" s="15"/>
       <c r="E168" s="15" t="s">
         <v>36</v>
       </c>
@@ -16698,17 +16690,19 @@
         <v>322</v>
       </c>
       <c r="B169" s="15" t="s">
-        <v>340</v>
+        <v>472</v>
       </c>
       <c r="C169" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="D169" s="15"/>
+      <c r="D169" s="15" t="s">
+        <v>341</v>
+      </c>
       <c r="E169" s="15" t="s">
-        <v>36</v>
+        <v>291</v>
       </c>
       <c r="F169" s="15" t="s">
-        <v>37</v>
+        <v>17</v>
       </c>
       <c r="G169" s="7">
         <v>46156</v>
@@ -16785,19 +16779,17 @@
         <v>322</v>
       </c>
       <c r="B170" s="15" t="s">
-        <v>474</v>
+        <v>342</v>
       </c>
       <c r="C170" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="D170" s="15" t="s">
-        <v>341</v>
-      </c>
+      <c r="D170" s="15"/>
       <c r="E170" s="15" t="s">
-        <v>291</v>
+        <v>36</v>
       </c>
       <c r="F170" s="15" t="s">
-        <v>17</v>
+        <v>37</v>
       </c>
       <c r="G170" s="7">
         <v>46156</v>
@@ -16871,15 +16863,17 @@
     </row>
     <row r="171" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A171" s="14" t="s">
-        <v>322</v>
+        <v>110</v>
       </c>
       <c r="B171" s="15" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="C171" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="D171" s="15"/>
+      <c r="D171" s="15" t="s">
+        <v>344</v>
+      </c>
       <c r="E171" s="15" t="s">
         <v>36</v>
       </c>
@@ -16887,16 +16881,16 @@
         <v>37</v>
       </c>
       <c r="G171" s="7">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="H171" s="8" t="s">
         <v>7</v>
       </c>
       <c r="I171" s="9" t="s">
-        <v>8</v>
+        <v>102</v>
       </c>
       <c r="J171" s="10" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="K171" s="10" t="s">
         <v>371</v>
@@ -16961,19 +16955,17 @@
         <v>110</v>
       </c>
       <c r="B172" s="15" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="C172" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="D172" s="15" t="s">
-        <v>344</v>
-      </c>
+      <c r="D172" s="15"/>
       <c r="E172" s="15" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="F172" s="15" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="G172" s="7">
         <v>46157</v>
@@ -17050,17 +17042,19 @@
         <v>110</v>
       </c>
       <c r="B173" s="15" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C173" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="D173" s="15"/>
+      <c r="D173" s="15" t="s">
+        <v>347</v>
+      </c>
       <c r="E173" s="15" t="s">
-        <v>40</v>
+        <v>348</v>
       </c>
       <c r="F173" s="15" t="s">
-        <v>41</v>
+        <v>81</v>
       </c>
       <c r="G173" s="7">
         <v>46157</v>
@@ -17134,22 +17128,20 @@
     </row>
     <row r="174" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A174" s="14" t="s">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="B174" s="15" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="C174" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="D174" s="15" t="s">
-        <v>347</v>
-      </c>
+      <c r="D174" s="15"/>
       <c r="E174" s="15" t="s">
-        <v>348</v>
+        <v>36</v>
       </c>
       <c r="F174" s="15" t="s">
-        <v>81</v>
+        <v>37</v>
       </c>
       <c r="G174" s="7">
         <v>46157</v>
@@ -17226,17 +17218,19 @@
         <v>100</v>
       </c>
       <c r="B175" s="15" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C175" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="D175" s="15"/>
+      <c r="D175" s="15" t="s">
+        <v>282</v>
+      </c>
       <c r="E175" s="15" t="s">
-        <v>36</v>
+        <v>187</v>
       </c>
       <c r="F175" s="15" t="s">
-        <v>37</v>
+        <v>351</v>
       </c>
       <c r="G175" s="7">
         <v>46157</v>
@@ -17313,19 +17307,19 @@
         <v>100</v>
       </c>
       <c r="B176" s="15" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="C176" s="16" t="s">
         <v>34</v>
       </c>
       <c r="D176" s="15" t="s">
-        <v>282</v>
+        <v>353</v>
       </c>
       <c r="E176" s="15" t="s">
-        <v>187</v>
+        <v>36</v>
       </c>
       <c r="F176" s="15" t="s">
-        <v>351</v>
+        <v>37</v>
       </c>
       <c r="G176" s="7">
         <v>46157</v>
@@ -17399,22 +17393,22 @@
     </row>
     <row r="177" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A177" s="14" t="s">
-        <v>100</v>
+        <v>220</v>
       </c>
       <c r="B177" s="15" t="s">
-        <v>352</v>
+        <v>473</v>
       </c>
       <c r="C177" s="16" t="s">
         <v>34</v>
       </c>
       <c r="D177" s="15" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="E177" s="15" t="s">
-        <v>36</v>
+        <v>75</v>
       </c>
       <c r="F177" s="15" t="s">
-        <v>37</v>
+        <v>76</v>
       </c>
       <c r="G177" s="7">
         <v>46157</v>
@@ -17487,53 +17481,53 @@
       <c r="BM177" s="4"/>
     </row>
     <row r="178" spans="1:65" x14ac:dyDescent="0.25">
-      <c r="A178" s="14" t="s">
+      <c r="A178" s="18" t="s">
         <v>220</v>
       </c>
-      <c r="B178" s="15" t="s">
+      <c r="B178" s="19" t="s">
+        <v>474</v>
+      </c>
+      <c r="C178" s="25" t="s">
+        <v>34</v>
+      </c>
+      <c r="D178" s="19" t="s">
         <v>475</v>
       </c>
-      <c r="C178" s="16" t="s">
-        <v>34</v>
-      </c>
-      <c r="D178" s="15" t="s">
-        <v>354</v>
-      </c>
-      <c r="E178" s="15" t="s">
-        <v>75</v>
-      </c>
-      <c r="F178" s="15" t="s">
-        <v>76</v>
-      </c>
-      <c r="G178" s="7">
+      <c r="E178" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="F178" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="G178" s="20">
         <v>46157</v>
       </c>
-      <c r="H178" s="8" t="s">
+      <c r="H178" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="I178" s="9" t="s">
+      <c r="I178" s="21" t="s">
         <v>102</v>
       </c>
-      <c r="J178" s="10" t="s">
+      <c r="J178" s="22" t="s">
         <v>65</v>
       </c>
-      <c r="K178" s="10" t="s">
+      <c r="K178" s="22" t="s">
         <v>371</v>
       </c>
-      <c r="L178" s="4"/>
-      <c r="M178" s="4"/>
-      <c r="N178" s="4"/>
-      <c r="O178" s="4"/>
-      <c r="P178" s="4"/>
-      <c r="Q178" s="4"/>
-      <c r="R178" s="4"/>
-      <c r="S178" s="4"/>
-      <c r="T178" s="4"/>
-      <c r="U178" s="4"/>
-      <c r="V178" s="4"/>
-      <c r="W178" s="4"/>
-      <c r="X178" s="4"/>
-      <c r="Y178" s="4"/>
+      <c r="L178" s="19"/>
+      <c r="M178" s="19"/>
+      <c r="N178" s="19"/>
+      <c r="O178" s="19"/>
+      <c r="P178" s="19"/>
+      <c r="Q178" s="19"/>
+      <c r="R178" s="19"/>
+      <c r="S178" s="19"/>
+      <c r="T178" s="19"/>
+      <c r="U178" s="19"/>
+      <c r="V178" s="19"/>
+      <c r="W178" s="19"/>
+      <c r="X178" s="19"/>
+      <c r="Y178" s="19"/>
       <c r="Z178" s="4"/>
       <c r="AA178" s="4"/>
       <c r="AB178" s="4"/>
@@ -17576,53 +17570,53 @@
       <c r="BM178" s="4"/>
     </row>
     <row r="179" spans="1:65" x14ac:dyDescent="0.25">
-      <c r="A179" s="18" t="s">
-        <v>220</v>
-      </c>
-      <c r="B179" s="19" t="s">
-        <v>476</v>
-      </c>
-      <c r="C179" s="25" t="s">
+      <c r="A179" s="14" t="s">
+        <v>209</v>
+      </c>
+      <c r="B179" s="15" t="s">
+        <v>355</v>
+      </c>
+      <c r="C179" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="D179" s="19" t="s">
-        <v>477</v>
-      </c>
-      <c r="E179" s="19" t="s">
-        <v>36</v>
-      </c>
-      <c r="F179" s="19" t="s">
-        <v>37</v>
-      </c>
-      <c r="G179" s="20">
+      <c r="D179" s="15" t="s">
+        <v>356</v>
+      </c>
+      <c r="E179" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="F179" s="15" t="s">
+        <v>76</v>
+      </c>
+      <c r="G179" s="7">
         <v>46157</v>
       </c>
-      <c r="H179" s="25" t="s">
+      <c r="H179" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="I179" s="21" t="s">
+      <c r="I179" s="9" t="s">
         <v>102</v>
       </c>
-      <c r="J179" s="22" t="s">
+      <c r="J179" s="10" t="s">
         <v>65</v>
       </c>
-      <c r="K179" s="22" t="s">
+      <c r="K179" s="10" t="s">
         <v>371</v>
       </c>
-      <c r="L179" s="19"/>
-      <c r="M179" s="19"/>
-      <c r="N179" s="19"/>
-      <c r="O179" s="19"/>
-      <c r="P179" s="19"/>
-      <c r="Q179" s="19"/>
-      <c r="R179" s="19"/>
-      <c r="S179" s="19"/>
-      <c r="T179" s="19"/>
-      <c r="U179" s="19"/>
-      <c r="V179" s="19"/>
-      <c r="W179" s="19"/>
-      <c r="X179" s="19"/>
-      <c r="Y179" s="19"/>
+      <c r="L179" s="4"/>
+      <c r="M179" s="4"/>
+      <c r="N179" s="4"/>
+      <c r="O179" s="4"/>
+      <c r="P179" s="4"/>
+      <c r="Q179" s="4"/>
+      <c r="R179" s="4"/>
+      <c r="S179" s="4"/>
+      <c r="T179" s="4"/>
+      <c r="U179" s="4"/>
+      <c r="V179" s="4"/>
+      <c r="W179" s="4"/>
+      <c r="X179" s="4"/>
+      <c r="Y179" s="4"/>
       <c r="Z179" s="4"/>
       <c r="AA179" s="4"/>
       <c r="AB179" s="4"/>
@@ -17665,39 +17659,17 @@
       <c r="BM179" s="4"/>
     </row>
     <row r="180" spans="1:65" x14ac:dyDescent="0.25">
-      <c r="A180" s="14" t="s">
-        <v>209</v>
-      </c>
-      <c r="B180" s="15" t="s">
-        <v>355</v>
-      </c>
-      <c r="C180" s="16" t="s">
-        <v>34</v>
-      </c>
-      <c r="D180" s="15" t="s">
-        <v>356</v>
-      </c>
-      <c r="E180" s="15" t="s">
-        <v>75</v>
-      </c>
-      <c r="F180" s="15" t="s">
-        <v>76</v>
-      </c>
-      <c r="G180" s="7">
-        <v>46157</v>
-      </c>
-      <c r="H180" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="I180" s="9" t="s">
-        <v>102</v>
-      </c>
-      <c r="J180" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="K180" s="10" t="s">
-        <v>371</v>
-      </c>
+      <c r="A180" s="4"/>
+      <c r="B180" s="4"/>
+      <c r="C180" s="4"/>
+      <c r="D180" s="4"/>
+      <c r="E180" s="4"/>
+      <c r="F180" s="4"/>
+      <c r="G180" s="4"/>
+      <c r="H180" s="4"/>
+      <c r="I180" s="4"/>
+      <c r="J180" s="4"/>
+      <c r="K180" s="4"/>
       <c r="L180" s="4"/>
       <c r="M180" s="4"/>
       <c r="N180" s="4"/>
@@ -18516,46 +18488,6 @@
       <c r="W192" s="4"/>
       <c r="X192" s="4"/>
       <c r="Y192" s="4"/>
-      <c r="Z192" s="4"/>
-      <c r="AA192" s="4"/>
-      <c r="AB192" s="4"/>
-      <c r="AC192" s="4"/>
-      <c r="AD192" s="4"/>
-      <c r="AE192" s="4"/>
-      <c r="AF192" s="4"/>
-      <c r="AG192" s="4"/>
-      <c r="AH192" s="4"/>
-      <c r="AI192" s="4"/>
-      <c r="AJ192" s="4"/>
-      <c r="AK192" s="4"/>
-      <c r="AL192" s="4"/>
-      <c r="AM192" s="4"/>
-      <c r="AN192" s="4"/>
-      <c r="AO192" s="4"/>
-      <c r="AP192" s="4"/>
-      <c r="AQ192" s="4"/>
-      <c r="AR192" s="4"/>
-      <c r="AS192" s="4"/>
-      <c r="AT192" s="4"/>
-      <c r="AU192" s="4"/>
-      <c r="AV192" s="4"/>
-      <c r="AW192" s="4"/>
-      <c r="AX192" s="4"/>
-      <c r="AY192" s="4"/>
-      <c r="AZ192" s="4"/>
-      <c r="BA192" s="4"/>
-      <c r="BB192" s="4"/>
-      <c r="BC192" s="4"/>
-      <c r="BD192" s="4"/>
-      <c r="BE192" s="4"/>
-      <c r="BF192" s="4"/>
-      <c r="BG192" s="4"/>
-      <c r="BH192" s="4"/>
-      <c r="BI192" s="4"/>
-      <c r="BJ192" s="4"/>
-      <c r="BK192" s="4"/>
-      <c r="BL192" s="4"/>
-      <c r="BM192" s="4"/>
     </row>
     <row r="193" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A193" s="4"/>
@@ -40130,42 +40062,15 @@
       <c r="X991" s="4"/>
       <c r="Y991" s="4"/>
     </row>
-    <row r="992" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A992" s="4"/>
-      <c r="B992" s="4"/>
-      <c r="C992" s="4"/>
-      <c r="D992" s="4"/>
-      <c r="E992" s="4"/>
-      <c r="F992" s="4"/>
-      <c r="G992" s="4"/>
-      <c r="H992" s="4"/>
-      <c r="I992" s="4"/>
-      <c r="J992" s="4"/>
-      <c r="K992" s="4"/>
-      <c r="L992" s="4"/>
-      <c r="M992" s="4"/>
-      <c r="N992" s="4"/>
-      <c r="O992" s="4"/>
-      <c r="P992" s="4"/>
-      <c r="Q992" s="4"/>
-      <c r="R992" s="4"/>
-      <c r="S992" s="4"/>
-      <c r="T992" s="4"/>
-      <c r="U992" s="4"/>
-      <c r="V992" s="4"/>
-      <c r="W992" s="4"/>
-      <c r="X992" s="4"/>
-      <c r="Y992" s="4"/>
-    </row>
   </sheetData>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G2:G180" xr:uid="{00000000-0002-0000-0100-000000000000}">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G2:G179" xr:uid="{00000000-0002-0000-0100-000000000000}">
       <formula1>"14/05/2026,15/05/2026"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="A2:A180" xr:uid="{00000000-0002-0000-0100-000001000000}">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="A2:A179" xr:uid="{00000000-0002-0000-0100-000001000000}">
       <formula1>"Football,Basket F,Basket H,Echecs,Babyfoot,Tennis de table,Rami,Running 5 km H,Running 5 km F,Running 10 km H,Running 10 km F,Tennis F,Tennis H,Padel,E-Sport FC26,E-Sport PUBG,Flechettes,Bras de Fer,Volley Ball,Billard"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="I2:I180" xr:uid="{00000000-0002-0000-0100-000002000000}">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="I2:I179" xr:uid="{00000000-0002-0000-0100-000002000000}">
       <formula1>"Sonarges,Inara,Club M'sallah,Forêt"</formula1>
     </dataValidation>
   </dataValidations>
